--- a/Storm Track Data.xlsx
+++ b/Storm Track Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolefrancis/Documents/GitHub/Final Project/hurricane_final_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{678DDD05-8EC1-3141-9B8D-C545215D6868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B587576-1023-4F4B-8652-3C3FA6B4BEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6180" yWindow="600" windowWidth="25160" windowHeight="19940" xr2:uid="{467F5656-0FC3-FB41-B06D-CA6FADCB6C5A}"/>
+    <workbookView xWindow="15440" yWindow="600" windowWidth="22500" windowHeight="19940" xr2:uid="{467F5656-0FC3-FB41-B06D-CA6FADCB6C5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>Strength</t>
   </si>
@@ -60,6 +60,30 @@
   </si>
   <si>
     <t>Classified</t>
+  </si>
+  <si>
+    <t>Francine</t>
+  </si>
+  <si>
+    <t>Ida</t>
+  </si>
+  <si>
+    <t>Claudette</t>
+  </si>
+  <si>
+    <t>Zeta</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>Cristobal</t>
+  </si>
+  <si>
+    <t>Barry</t>
+  </si>
+  <si>
+    <t>Nate</t>
   </si>
 </sst>
 </file>
@@ -117,10 +141,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -440,13 +460,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC92FAA3-B592-3C4A-965D-EBC20A0506DF}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -469,7 +489,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>45547</v>
       </c>
@@ -491,8 +511,11 @@
       <c r="G2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>44437.666666666664</v>
       </c>
@@ -514,8 +537,11 @@
       <c r="G3">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>44366.25</v>
       </c>
@@ -537,8 +563,11 @@
       <c r="G4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>44132.875</v>
       </c>
@@ -560,10 +589,13 @@
       <c r="G5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>44798</v>
+        <v>44068</v>
       </c>
       <c r="B6">
         <v>28.9</v>
@@ -583,8 +615,11 @@
       <c r="G6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>43989.916666666664</v>
       </c>
@@ -606,8 +641,11 @@
       <c r="G7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>43658.75</v>
       </c>
@@ -629,8 +667,11 @@
       <c r="G8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>43016</v>
       </c>
@@ -651,6 +692,9 @@
       </c>
       <c r="G9">
         <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Storm Track Data.xlsx
+++ b/Storm Track Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolefrancis/Documents/GitHub/Final Project/hurricane_final_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B587576-1023-4F4B-8652-3C3FA6B4BEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B9B60F-62CE-B846-B220-E1111BB8DCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15440" yWindow="600" windowWidth="22500" windowHeight="19940" xr2:uid="{467F5656-0FC3-FB41-B06D-CA6FADCB6C5A}"/>
+    <workbookView xWindow="18180" yWindow="600" windowWidth="17660" windowHeight="19940" xr2:uid="{467F5656-0FC3-FB41-B06D-CA6FADCB6C5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -520,10 +520,10 @@
         <v>44437.666666666664</v>
       </c>
       <c r="B3">
-        <v>21.5</v>
+        <v>29.1</v>
       </c>
       <c r="C3">
-        <v>82.6</v>
+        <v>90.2</v>
       </c>
       <c r="D3">
         <v>4</v>

--- a/Storm Track Data.xlsx
+++ b/Storm Track Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolefrancis/Documents/GitHub/Final Project/hurricane_final_project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarar/Documents/Semester 8/environmental data analysis/hurricane_final_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B9B60F-62CE-B846-B220-E1111BB8DCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775AFAC9-0D19-BE41-AA7B-BD9F47D40811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18180" yWindow="600" windowWidth="17660" windowHeight="19940" xr2:uid="{467F5656-0FC3-FB41-B06D-CA6FADCB6C5A}"/>
+    <workbookView xWindow="11740" yWindow="740" windowWidth="17660" windowHeight="16920" xr2:uid="{467F5656-0FC3-FB41-B06D-CA6FADCB6C5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,28 +62,28 @@
     <t>Classified</t>
   </si>
   <si>
-    <t>Francine</t>
-  </si>
-  <si>
-    <t>Ida</t>
-  </si>
-  <si>
-    <t>Claudette</t>
-  </si>
-  <si>
-    <t>Zeta</t>
-  </si>
-  <si>
-    <t>Marco</t>
-  </si>
-  <si>
-    <t>Cristobal</t>
-  </si>
-  <si>
-    <t>Barry</t>
-  </si>
-  <si>
-    <t>Nate</t>
+    <t>Francine (H1)</t>
+  </si>
+  <si>
+    <t>Ida (H4)</t>
+  </si>
+  <si>
+    <t>Claudette (TS)</t>
+  </si>
+  <si>
+    <t>Zeta (H3)</t>
+  </si>
+  <si>
+    <t>Marco (TS)</t>
+  </si>
+  <si>
+    <t>Cristobal (TS)</t>
+  </si>
+  <si>
+    <t>Barry (TS)</t>
+  </si>
+  <si>
+    <t>Nate (H1)</t>
   </si>
 </sst>
 </file>
